--- a/artfynd/A 50248-2025 artfynd.xlsx
+++ b/artfynd/A 50248-2025 artfynd.xlsx
@@ -2543,12 +2543,7 @@
         <v>106474398</v>
       </c>
       <c r="B17" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2586,23 +2581,23 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 97 m NE, Upl</t>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 35 m SE, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623798</v>
+        <v>623754</v>
       </c>
       <c r="R17" t="n">
-        <v>6680194</v>
+        <v>6680130</v>
       </c>
       <c r="S17" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/artfynd/A 50248-2025 artfynd.xlsx
+++ b/artfynd/A 50248-2025 artfynd.xlsx
@@ -2543,7 +2543,7 @@
         <v>106474398</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 50248-2025 artfynd.xlsx
+++ b/artfynd/A 50248-2025 artfynd.xlsx
@@ -2543,7 +2543,7 @@
         <v>106474398</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 50248-2025 artfynd.xlsx
+++ b/artfynd/A 50248-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64527235</v>
+        <v>103870826</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långhällsmossen, Upl</t>
+          <t>syd Långhällsmossen NR, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623823.0548160616</v>
+        <v>623716</v>
       </c>
       <c r="R2" t="n">
-        <v>6680251.552014777</v>
+        <v>6680359</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-03-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-03-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,48 +756,53 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>brunmurken granlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Klas Rådberg</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Rådberg, Ola Ejdrén, Mikael Rosén</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64527243</v>
+        <v>98756266</v>
       </c>
       <c r="B3" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>100045</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,22 +812,30 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långhällsmossen, Upl</t>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 97 m NE, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623823.0548160616</v>
+        <v>623798</v>
       </c>
       <c r="R3" t="n">
-        <v>6680251.552014777</v>
+        <v>6680194</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +859,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-03-19</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-03-19</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,12 +889,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Klas Rådberg</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Klas Rådberg, Ola Ejdrén, Mikael Rosén</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -910,16 +904,11 @@
         <v>98475594</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -959,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623830.9526196178</v>
+        <v>623831</v>
       </c>
       <c r="R4" t="n">
-        <v>6680106.699287759</v>
+        <v>6680107</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1031,37 +1020,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98588454</v>
+        <v>98588433</v>
       </c>
       <c r="B5" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1083,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623753.5012225329</v>
+        <v>623754</v>
       </c>
       <c r="R5" t="n">
-        <v>6680129.918040249</v>
+        <v>6680130</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1155,32 +1139,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98588433</v>
+        <v>64527243</v>
       </c>
       <c r="B6" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100067</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1193,27 +1172,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 35 m SE, Upl</t>
+          <t>Långhällsmossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623753.5012225329</v>
+        <v>623823</v>
       </c>
       <c r="R6" t="n">
-        <v>6680129.918040249</v>
+        <v>6680252</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,22 +1208,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-02-12</t>
+          <t>2017-03-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-02-12</t>
+          <t>2017-03-19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,27 +1238,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kalle Brinell</t>
+          <t>Klas Rådberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kalle Brinell</t>
+          <t>Klas Rådberg, Ola Ejdrén, Mikael Rosén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98756301</v>
+        <v>82651871</v>
       </c>
       <c r="B7" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,49 +1261,53 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 97 m NE, Upl</t>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 35 m SE, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623798.1056312879</v>
+        <v>623754</v>
       </c>
       <c r="R7" t="n">
-        <v>6680194.547315476</v>
+        <v>6680130</v>
       </c>
       <c r="S7" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,22 +1331,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:20</t>
+          <t>2020-03-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:22</t>
+          <t>2020-03-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,15 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103870826</v>
+        <v>64527234</v>
       </c>
       <c r="B8" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,34 +1374,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>syd Långhällsmossen NR, Upl</t>
+          <t>Långhällsmossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623715.8639309421</v>
+        <v>623823</v>
       </c>
       <c r="R8" t="n">
-        <v>6680359.240798196</v>
+        <v>6680252</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,22 +1437,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2017-03-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2017-03-19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,84 +1463,72 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>brunmurken granlåga</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Klas Rådberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Klas Rådberg, Ola Ejdrén, Mikael Rosén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103870832</v>
+        <v>91733026</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>syd Långhällsmossen NR, Upl</t>
+          <t>Hornbäcken SO, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623809.3208559668</v>
+        <v>623741</v>
       </c>
       <c r="R9" t="n">
-        <v>6680010.541178032</v>
+        <v>6680085</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1600,27 +1552,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2021-03-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2021-03-20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>&lt;1 kvm</t>
+          <t>4 korvar på grusväg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1632,35 +1584,35 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Väg</t>
+        </is>
+      </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>äldre barrskog</t>
+          <t>grusväg genom barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103870829</v>
+        <v>91733050</v>
       </c>
       <c r="B10" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,42 +1620,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>syd Långhällsmossen NR, Upl</t>
+          <t>Hornbäcken OSO, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623719.837028494</v>
+        <v>623782</v>
       </c>
       <c r="R10" t="n">
-        <v>6680300.733351685</v>
+        <v>6680164</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1727,22 +1682,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2021-03-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2021-03-20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 korvar på grusväg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1754,40 +1714,35 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Väg</t>
+        </is>
+      </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>torrgran</t>
+          <t>grusväg genom barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103870825</v>
+        <v>103870829</v>
       </c>
       <c r="B11" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,21 +1750,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1824,10 +1779,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623694.3990859864</v>
+        <v>623720</v>
       </c>
       <c r="R11" t="n">
-        <v>6680258.125993789</v>
+        <v>6680301</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1857,19 +1812,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1906,37 +1851,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103870833</v>
+        <v>103870825</v>
       </c>
       <c r="B12" t="n">
-        <v>5112</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102204</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1951,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623763.4936698705</v>
+        <v>623694</v>
       </c>
       <c r="R12" t="n">
-        <v>6679967.239007951</v>
+        <v>6680258</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1984,21 +1924,11 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2015,7 +1945,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>grov grangren</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2033,43 +1963,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103870831</v>
+        <v>103870830</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2078,10 +2003,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623794.103713295</v>
+        <v>623720</v>
       </c>
       <c r="R13" t="n">
-        <v>6680077.618213482</v>
+        <v>6680301</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2111,26 +2036,11 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>&lt;1 kvm</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2143,6 +2053,11 @@
       <c r="AI13" t="inlineStr">
         <is>
           <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2160,43 +2075,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103870827</v>
+        <v>103870833</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>102204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2205,10 +2115,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623715.8639309421</v>
+        <v>623763</v>
       </c>
       <c r="R14" t="n">
-        <v>6680359.240798196</v>
+        <v>6679967</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2238,26 +2148,11 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>&lt;1 kvm</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2270,6 +2165,11 @@
       <c r="AI14" t="inlineStr">
         <is>
           <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>grov grangren</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2287,15 +2187,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103870830</v>
+        <v>99090285</v>
       </c>
       <c r="B15" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,42 +2198,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>syd Långhällsmossen NR, Upl</t>
+          <t>Nyckelmyren, Området Toften - Långhällsmossen, Upl 578 m NE, Området Toften - Långhällsmossen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623719.837028494</v>
+        <v>623729</v>
       </c>
       <c r="R15" t="n">
-        <v>6680300.733351685</v>
+        <v>6680062</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2362,22 +2264,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-03-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-03-13</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2388,41 +2290,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>torrgran</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Jonas Melin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Jonas Melin, Jörgen Eriksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103870828</v>
+        <v>123659764</v>
       </c>
       <c r="B16" t="n">
-        <v>6202</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2430,16 +2317,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105336</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2449,22 +2336,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>syd Långhällsmossen NR, Upl</t>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623727.3862488425</v>
+        <v>623735</v>
       </c>
       <c r="R16" t="n">
-        <v>6680386.467007534</v>
+        <v>6679978</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2488,22 +2380,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2514,36 +2406,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Ulf Elman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Ulf Elman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106474398</v>
+        <v>123659774</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>58497</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,16 +2433,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102990</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2568,36 +2450,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 35 m SE, Upl</t>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623754</v>
+        <v>623735</v>
       </c>
       <c r="R17" t="n">
-        <v>6680130</v>
+        <v>6679978</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2621,22 +2492,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2651,44 +2522,39 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kalle Brinell</t>
+          <t>Ulf Elman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kalle Brinell</t>
+          <t>Ulf Elman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>99090285</v>
+        <v>98588461</v>
       </c>
       <c r="B18" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2698,30 +2564,30 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nyckelmyren, Området Toften - Långhällsmossen, Upl 578 m NE, Området Toften - Långhällsmossen, Upl</t>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 35 m SE, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623728.4395806014</v>
+        <v>623754</v>
       </c>
       <c r="R18" t="n">
-        <v>6680061.477222367</v>
+        <v>6680130</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2745,22 +2611,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-03-13</t>
+          <t>2022-02-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-03-13</t>
+          <t>2022-02-12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2775,44 +2641,39 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jonas Melin</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jonas Melin, Jörgen Eriksson</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123659764</v>
+        <v>123659780</v>
       </c>
       <c r="B19" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2820,11 +2681,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -2871,7 +2728,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>05:57</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2881,7 +2738,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>05:57</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2908,58 +2765,52 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123659776</v>
+        <v>64527235</v>
       </c>
       <c r="B20" t="n">
-        <v>58191</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl</t>
+          <t>Långhällsmossen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623735</v>
+        <v>623823</v>
       </c>
       <c r="R20" t="n">
-        <v>6679978</v>
+        <v>6680252</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2983,22 +2834,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2017-03-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2017-03-19</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3013,70 +2864,72 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulf Elman</t>
+          <t>Klas Rådberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulf Elman</t>
+          <t>Klas Rådberg, Ola Ejdrén, Mikael Rosén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123659780</v>
+        <v>98588454</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl</t>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 35 m SE, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623735</v>
+        <v>623754</v>
       </c>
       <c r="R21" t="n">
-        <v>6679978</v>
+        <v>6680130</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3100,22 +2953,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2022-02-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2022-02-12</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3130,70 +2983,72 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulf Elman</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulf Elman</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123659774</v>
+        <v>98756301</v>
       </c>
       <c r="B22" t="n">
-        <v>58055</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102990</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl</t>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 97 m NE, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623735</v>
+        <v>623798</v>
       </c>
       <c r="R22" t="n">
-        <v>6679978</v>
+        <v>6680194</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3217,22 +3072,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3247,15 +3102,924 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>98588477</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 35 m SE, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>623754</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6680130</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-02-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-02-12</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>98756351</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 97 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>623798</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6680194</v>
+      </c>
+      <c r="S24" t="n">
+        <v>74</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123659776</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>623735</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6679978</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>06:03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>06:03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Ulf Elman</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Ulf Elman</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>103870828</v>
+      </c>
+      <c r="B26" t="n">
+        <v>6274</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>syd Långhällsmossen NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>623727</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6680386</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>103870823</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>syd Långhällsmossen NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>623732</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6680206</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>103870827</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>syd Långhällsmossen NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>623716</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6680359</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>&lt;1 kvm</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>103870831</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>syd Långhällsmossen NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>623794</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6680078</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>&lt;1 kvm</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>103870832</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>syd Långhällsmossen NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>623809</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6680011</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>&lt;1 kvm</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50248-2025 artfynd.xlsx
+++ b/artfynd/A 50248-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870826</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98756266</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98475594</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98588433</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64527243</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1390,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82651871</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1476,6 +1511,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64527234</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1606,6 +1646,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91733026</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1736,6 +1781,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91733050</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1848,6 +1898,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870829</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1960,6 +2015,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870825</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2072,6 +2132,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870830</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2184,6 +2249,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870833</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2303,6 +2373,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99090285</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2419,6 +2494,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123659764</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2531,6 +2611,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123659774</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2650,6 +2735,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98588461</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2762,6 +2852,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123659780</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2873,6 +2968,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64527235</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2992,6 +3092,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98588454</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3111,6 +3216,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98756301</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3230,6 +3340,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98588477</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3349,6 +3464,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98756351</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3461,6 +3581,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123659776</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3572,6 +3697,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870828</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3684,6 +3814,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870823</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3796,6 +3931,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870827</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3908,6 +4048,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870831</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4020,8 +4165,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870832</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>